--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>section-landing-hero-cards</t>
   </si>
   <si>
-    <t>2026-06-12T19:29:02.828Z</t>
+    <t>2026-06-13T17:19:48.204Z</t>
   </si>
   <si>
     <t>About Banner Health | Leading Nonprofit Health System</t>
@@ -73,7 +73,7 @@
     <t>search-listing</t>
   </si>
   <si>
-    <t>2026-06-12T19:35:29.169Z</t>
+    <t>2026-06-13T17:20:00.518Z</t>
   </si>
   <si>
     <t>Calendar of Events | Banner Health</t>
@@ -91,7 +91,7 @@
     <t>careers</t>
   </si>
   <si>
-    <t>2026-06-12T19:29:11.020Z</t>
+    <t>2026-06-13T17:19:54.287Z</t>
   </si>
   <si>
     <t>Health Care Careers</t>
@@ -109,7 +109,7 @@
     <t>contact-us</t>
   </si>
   <si>
-    <t>2026-06-12T19:35:34.203Z</t>
+    <t>2026-06-13T17:20:06.213Z</t>
   </si>
   <si>
     <t>Contact Us | Banner Health</t>
@@ -127,7 +127,7 @@
     <t>getcarenow</t>
   </si>
   <si>
-    <t>2026-06-12T19:29:31.941Z</t>
+    <t>2026-06-13T17:34:19.714Z</t>
   </si>
   <si>
     <t>Obtenga atención ahora | Banner Health</t>
@@ -145,10 +145,10 @@
     <t>health-professionals</t>
   </si>
   <si>
-    <t>2026-06-12T19:29:38.871Z</t>
-  </si>
-  <si>
-    <t>Para Profesionales de la Salud</t>
+    <t>2026-06-13T17:33:55.202Z</t>
+  </si>
+  <si>
+    <t>For Health Professionals</t>
   </si>
   <si>
     <t>https://www.bannerhealth.com/health-professionals</t>
@@ -160,7 +160,7 @@
     <t>healthcareblog</t>
   </si>
   <si>
-    <t>2026-06-12T19:35:57.457Z</t>
+    <t>2026-06-12T20:23:53.623Z</t>
   </si>
   <si>
     <t>Banner Health Blog</t>
@@ -181,7 +181,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-12T20:22:16.298Z</t>
+    <t>2026-06-13T17:56:02.540Z</t>
   </si>
   <si>
     <t>Banner Health | Health Care Made Easier in AZ, CO, WY, NE, NV, CA</t>
@@ -196,7 +196,7 @@
     <t>insurance</t>
   </si>
   <si>
-    <t>2026-06-12T19:29:43.354Z</t>
+    <t>2026-06-13T17:34:30.242Z</t>
   </si>
   <si>
     <t>Planes y redes Banner | Banner Health</t>
@@ -217,7 +217,7 @@
     <t>breadcrumb-partner-content</t>
   </si>
   <si>
-    <t>2026-06-12T20:17:03.522Z</t>
+    <t>2026-06-13T17:20:21.038Z</t>
   </si>
   <si>
     <t>Kaiser Permanenete | Banner Health</t>
@@ -235,7 +235,7 @@
     <t>locations</t>
   </si>
   <si>
-    <t>2026-06-12T19:35:23.342Z</t>
+    <t>2026-06-13T17:20:14.706Z</t>
   </si>
   <si>
     <t>Our Locations | Banner Health</t>
@@ -253,7 +253,7 @@
     <t>medicare</t>
   </si>
   <si>
-    <t>2026-06-12T19:36:02.504Z</t>
+    <t>2026-06-12T20:24:01.268Z</t>
   </si>
   <si>
     <t>Banner Medicare</t>
@@ -274,7 +274,7 @@
     <t>cards-landing</t>
   </si>
   <si>
-    <t>2026-06-12T20:09:41.073Z</t>
+    <t>2026-06-12T20:24:51.841Z</t>
   </si>
   <si>
     <t>Banner Network Colorado</t>
@@ -292,7 +292,7 @@
     <t>networksouth</t>
   </si>
   <si>
-    <t>2026-06-12T19:36:08.318Z</t>
+    <t>2026-06-12T20:24:07.134Z</t>
   </si>
   <si>
     <t>Banner Network Southern Arizona</t>
@@ -307,7 +307,7 @@
     <t>newsroom</t>
   </si>
   <si>
-    <t>2026-06-12T19:36:14.536Z</t>
+    <t>2026-06-12T20:24:14.980Z</t>
   </si>
   <si>
     <t>Banner Health | Newsroom and Media Resource Center</t>
@@ -325,7 +325,7 @@
     <t>physician-directory</t>
   </si>
   <si>
-    <t>2026-06-12T20:09:57.871Z</t>
+    <t>2026-06-13T17:20:26.802Z</t>
   </si>
   <si>
     <t>Find a Doctor</t>
@@ -340,7 +340,7 @@
     <t>search-results</t>
   </si>
   <si>
-    <t>2026-06-12T20:09:01.982Z</t>
+    <t>2026-06-13T17:20:32.734Z</t>
   </si>
   <si>
     <t>Banner Health Search Results | Banner Health</t>
@@ -358,7 +358,7 @@
     <t>hero-landing</t>
   </si>
   <si>
-    <t>2026-06-12T20:21:51.186Z</t>
+    <t>2026-06-13T17:20:38.563Z</t>
   </si>
   <si>
     <t>Services</t>
@@ -373,7 +373,7 @@
     <t>staying-well</t>
   </si>
   <si>
-    <t>2026-06-12T19:29:49.326Z</t>
+    <t>2026-06-13T17:34:24.098Z</t>
   </si>
   <si>
     <t>Ayúdame a estar bien | Banner Health</t>
@@ -388,7 +388,7 @@
     <t>es/about</t>
   </si>
   <si>
-    <t>2026-06-12T19:29:16.478Z</t>
+    <t>2026-06-13T17:34:02.450Z</t>
   </si>
   <si>
     <t>Acerca de Banner Health | Sistema líder de salud sin fines de lucro</t>
@@ -403,7 +403,7 @@
     <t>es/calendar</t>
   </si>
   <si>
-    <t>2026-06-12T19:35:41.013Z</t>
+    <t>2026-06-13T17:35:09.920Z</t>
   </si>
   <si>
     <t>Calendario de Eventos | Banner Health</t>
@@ -418,7 +418,7 @@
     <t>es/careers</t>
   </si>
   <si>
-    <t>2026-06-12T19:29:22.089Z</t>
+    <t>2026-06-13T17:34:08.199Z</t>
   </si>
   <si>
     <t>Carreras de atención médica</t>
@@ -433,7 +433,7 @@
     <t>es/contact-us</t>
   </si>
   <si>
-    <t>2026-06-12T19:35:45.218Z</t>
+    <t>2026-06-13T17:34:54.256Z</t>
   </si>
   <si>
     <t>Contáctenos | Banner Health</t>
@@ -451,7 +451,7 @@
     <t>breadcrumb-content</t>
   </si>
   <si>
-    <t>2026-06-12T20:10:06.210Z</t>
+    <t>2026-06-13T17:34:43.159Z</t>
   </si>
   <si>
     <t>https://www.bannerhealth.com/es/getcarenow</t>
@@ -469,7 +469,7 @@
     <t>service-detail-cards-carousel</t>
   </si>
   <si>
-    <t>2026-06-12T20:16:54.759Z</t>
+    <t>2026-06-12T20:24:29.542Z</t>
   </si>
   <si>
     <t>Blog de Banner Health</t>
@@ -484,7 +484,7 @@
     <t>es/kaiser-permanente</t>
   </si>
   <si>
-    <t>2026-06-12T20:17:09.648Z</t>
+    <t>2026-06-13T17:34:37.143Z</t>
   </si>
   <si>
     <t>Káiser Permanente | Banner Health</t>
@@ -499,7 +499,7 @@
     <t>es/locations</t>
   </si>
   <si>
-    <t>2026-06-12T19:35:52.021Z</t>
+    <t>2026-06-13T17:35:03.037Z</t>
   </si>
   <si>
     <t>Nuestras Ubicaciones | Banner Health</t>
@@ -514,7 +514,7 @@
     <t>es/medicare</t>
   </si>
   <si>
-    <t>2026-06-12T20:16:50.204Z</t>
+    <t>2026-06-12T20:24:24.934Z</t>
   </si>
   <si>
     <t>https://www.bannerhealth.com/es/medicare</t>
@@ -529,7 +529,7 @@
     <t>directory-breadcrumb</t>
   </si>
   <si>
-    <t>2026-06-12T20:09:49.738Z</t>
+    <t>2026-06-13T17:35:20.866Z</t>
   </si>
   <si>
     <t>Encuentre un médico</t>
@@ -544,7 +544,7 @@
     <t>es/search-results</t>
   </si>
   <si>
-    <t>2026-06-12T20:09:08.403Z</t>
+    <t>2026-06-13T17:34:48.850Z</t>
   </si>
   <si>
     <t>Resultados de la búsqueda de Banner Health | Banner Health</t>
@@ -559,7 +559,7 @@
     <t>es/services</t>
   </si>
   <si>
-    <t>2026-06-12T20:21:57.157Z</t>
+    <t>2026-06-13T17:35:15.381Z</t>
   </si>
   <si>
     <t>Servicios</t>
@@ -574,7 +574,7 @@
     <t>es/staying-well</t>
   </si>
   <si>
-    <t>2026-06-12T19:29:26.454Z</t>
+    <t>2026-06-13T17:34:14.379Z</t>
   </si>
   <si>
     <t>https://www.bannerhealth.com/es/staying-well</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="190">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>section-landing-hero-cards</t>
   </si>
   <si>
-    <t>2026-06-13T17:19:48.204Z</t>
+    <t>2026-06-13T17:56:08.440Z</t>
   </si>
   <si>
     <t>About Banner Health | Leading Nonprofit Health System</t>
@@ -73,7 +73,7 @@
     <t>search-listing</t>
   </si>
   <si>
-    <t>2026-06-13T17:20:00.518Z</t>
+    <t>2026-06-13T17:57:04.270Z</t>
   </si>
   <si>
     <t>Calendar of Events | Banner Health</t>
@@ -85,280 +85,289 @@
     <t>careers.report.json</t>
   </si>
   <si>
+    <t>["hero","accordion","personas","cards-feature","cards-feature","cards-feature"]</t>
+  </si>
+  <si>
+    <t>careers</t>
+  </si>
+  <si>
+    <t>2026-06-15T19:29:33.230Z</t>
+  </si>
+  <si>
+    <t>Health Care Careers</t>
+  </si>
+  <si>
+    <t>https://www.bannerhealth.com/careers</t>
+  </si>
+  <si>
+    <t>contact-us.report.json</t>
+  </si>
+  <si>
+    <t>["cards-feature"]</t>
+  </si>
+  <si>
+    <t>contact-us</t>
+  </si>
+  <si>
+    <t>2026-06-13T17:57:10.277Z</t>
+  </si>
+  <si>
+    <t>Contact Us | Banner Health</t>
+  </si>
+  <si>
+    <t>https://www.bannerhealth.com/contact-us</t>
+  </si>
+  <si>
+    <t>getcarenow.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature"]</t>
+  </si>
+  <si>
+    <t>getcarenow</t>
+  </si>
+  <si>
+    <t>2026-06-13T17:56:37.918Z</t>
+  </si>
+  <si>
+    <t>Obtenga atención ahora | Banner Health</t>
+  </si>
+  <si>
+    <t>https://www.bannerhealth.com/getcarenow</t>
+  </si>
+  <si>
+    <t>health-professionals.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards-feature","cards-feature"]</t>
+  </si>
+  <si>
+    <t>health-professionals</t>
+  </si>
+  <si>
+    <t>2026-06-13T17:56:42.763Z</t>
+  </si>
+  <si>
+    <t>Para Profesionales de la Salud</t>
+  </si>
+  <si>
+    <t>https://www.bannerhealth.com/health-professionals</t>
+  </si>
+  <si>
+    <t>healthcareblog.report.json</t>
+  </si>
+  <si>
+    <t>["feature-articles","carousel","cards-feature","cards-feature","cards-feature"]</t>
+  </si>
+  <si>
+    <t>healthcareblog</t>
+  </si>
+  <si>
+    <t>service-detail-cards-carousel</t>
+  </si>
+  <si>
+    <t>2026-06-14T21:02:23.100Z</t>
+  </si>
+  <si>
+    <t>Banner Health Blog</t>
+  </si>
+  <si>
+    <t>https://www.bannerhealth.com/healthcareblog</t>
+  </si>
+  <si>
+    <t>index.report.json</t>
+  </si>
+  <si>
+    <t>["cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature"]</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>homepage</t>
+  </si>
+  <si>
+    <t>2026-06-16T18:06:48.635Z</t>
+  </si>
+  <si>
+    <t>Banner Health | Health Care Made Easier in AZ, CO, WY, NE, NV, CA</t>
+  </si>
+  <si>
+    <t>https://www.bannerhealth.com/</t>
+  </si>
+  <si>
+    <t>insurance.report.json</t>
+  </si>
+  <si>
+    <t>insurance</t>
+  </si>
+  <si>
+    <t>2026-06-13T17:56:47.788Z</t>
+  </si>
+  <si>
+    <t>Planes y redes Banner | Banner Health</t>
+  </si>
+  <si>
+    <t>https://www.bannerhealth.com/insurance</t>
+  </si>
+  <si>
+    <t>kaiser-permanente.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards-feature"]</t>
+  </si>
+  <si>
+    <t>kaiser-permanente</t>
+  </si>
+  <si>
+    <t>breadcrumb-partner-content</t>
+  </si>
+  <si>
+    <t>2026-06-13T17:58:30.137Z</t>
+  </si>
+  <si>
+    <t>Kaiser Permanenete | Banner Health</t>
+  </si>
+  <si>
+    <t>https://www.bannerhealth.com/kaiser-permanente</t>
+  </si>
+  <si>
+    <t>locations.report.json</t>
+  </si>
+  <si>
+    <t>["search"]</t>
+  </si>
+  <si>
+    <t>locations</t>
+  </si>
+  <si>
+    <t>2026-06-13T17:56:58.070Z</t>
+  </si>
+  <si>
+    <t>Our Locations | Banner Health</t>
+  </si>
+  <si>
+    <t>https://www.bannerhealth.com/locations</t>
+  </si>
+  <si>
+    <t>medicare.report.json</t>
+  </si>
+  <si>
+    <t>["cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature"]</t>
+  </si>
+  <si>
+    <t>medicare</t>
+  </si>
+  <si>
+    <t>2026-06-13T17:57:39.124Z</t>
+  </si>
+  <si>
+    <t>Banner Medicare</t>
+  </si>
+  <si>
+    <t>https://www.bannerhealth.com/medicare</t>
+  </si>
+  <si>
+    <t>networkcolorado.report.json</t>
+  </si>
+  <si>
+    <t>["cards-feature","cards-feature"]</t>
+  </si>
+  <si>
+    <t>networkcolorado</t>
+  </si>
+  <si>
+    <t>cards-landing</t>
+  </si>
+  <si>
+    <t>2026-06-13T17:58:41.927Z</t>
+  </si>
+  <si>
+    <t>Banner Network Colorado</t>
+  </si>
+  <si>
+    <t>https://www.bannerhealth.com/networkcolorado</t>
+  </si>
+  <si>
+    <t>networksouth.report.json</t>
+  </si>
+  <si>
+    <t>["cards-feature","cards-feature","cards-feature"]</t>
+  </si>
+  <si>
+    <t>networksouth</t>
+  </si>
+  <si>
+    <t>2026-06-13T17:57:45.591Z</t>
+  </si>
+  <si>
+    <t>Banner Network Southern Arizona</t>
+  </si>
+  <si>
+    <t>https://www.bannerhealth.com/networksouth</t>
+  </si>
+  <si>
+    <t>newsroom.report.json</t>
+  </si>
+  <si>
+    <t>newsroom</t>
+  </si>
+  <si>
+    <t>2026-06-13T17:57:52.876Z</t>
+  </si>
+  <si>
+    <t>Banner Health | Newsroom and Media Resource Center</t>
+  </si>
+  <si>
+    <t>https://www.bannerhealth.com/newsroom</t>
+  </si>
+  <si>
+    <t>physician-directory.report.json</t>
+  </si>
+  <si>
+    <t>["search","cards-feature","cards-feature"]</t>
+  </si>
+  <si>
+    <t>physician-directory</t>
+  </si>
+  <si>
+    <t>2026-06-13T17:58:51.545Z</t>
+  </si>
+  <si>
+    <t>Find a Doctor</t>
+  </si>
+  <si>
+    <t>https://www.bannerhealth.com/physician-directory</t>
+  </si>
+  <si>
+    <t>search-results.report.json</t>
+  </si>
+  <si>
+    <t>search-results</t>
+  </si>
+  <si>
+    <t>2026-06-13T17:20:32.734Z</t>
+  </si>
+  <si>
+    <t>Banner Health Search Results | Banner Health</t>
+  </si>
+  <si>
+    <t>https://www.bannerhealth.com/search-results</t>
+  </si>
+  <si>
+    <t>services.report.json</t>
+  </si>
+  <si>
     <t>["cards-feature","cards-feature","cards-feature","cards-feature"]</t>
   </si>
   <si>
-    <t>careers</t>
-  </si>
-  <si>
-    <t>2026-06-13T17:19:54.287Z</t>
-  </si>
-  <si>
-    <t>Health Care Careers</t>
-  </si>
-  <si>
-    <t>https://www.bannerhealth.com/careers</t>
-  </si>
-  <si>
-    <t>contact-us.report.json</t>
-  </si>
-  <si>
-    <t>["cards-feature"]</t>
-  </si>
-  <si>
-    <t>contact-us</t>
-  </si>
-  <si>
-    <t>2026-06-13T17:20:06.213Z</t>
-  </si>
-  <si>
-    <t>Contact Us | Banner Health</t>
-  </si>
-  <si>
-    <t>https://www.bannerhealth.com/contact-us</t>
-  </si>
-  <si>
-    <t>getcarenow.report.json</t>
-  </si>
-  <si>
-    <t>["hero","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature"]</t>
-  </si>
-  <si>
-    <t>getcarenow</t>
-  </si>
-  <si>
-    <t>2026-06-13T17:34:19.714Z</t>
-  </si>
-  <si>
-    <t>Obtenga atención ahora | Banner Health</t>
-  </si>
-  <si>
-    <t>https://www.bannerhealth.com/getcarenow</t>
-  </si>
-  <si>
-    <t>health-professionals.report.json</t>
-  </si>
-  <si>
-    <t>["hero","cards-feature","cards-feature"]</t>
-  </si>
-  <si>
-    <t>health-professionals</t>
-  </si>
-  <si>
-    <t>2026-06-13T17:33:55.202Z</t>
-  </si>
-  <si>
-    <t>For Health Professionals</t>
-  </si>
-  <si>
-    <t>https://www.bannerhealth.com/health-professionals</t>
-  </si>
-  <si>
-    <t>healthcareblog.report.json</t>
-  </si>
-  <si>
-    <t>healthcareblog</t>
-  </si>
-  <si>
-    <t>2026-06-12T20:23:53.623Z</t>
-  </si>
-  <si>
-    <t>Banner Health Blog</t>
-  </si>
-  <si>
-    <t>https://www.bannerhealth.com/healthcareblog</t>
-  </si>
-  <si>
-    <t>index.report.json</t>
-  </si>
-  <si>
-    <t>["cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature"]</t>
-  </si>
-  <si>
-    <t>index</t>
-  </si>
-  <si>
-    <t>homepage</t>
-  </si>
-  <si>
-    <t>2026-06-13T17:56:02.540Z</t>
-  </si>
-  <si>
-    <t>Banner Health | Health Care Made Easier in AZ, CO, WY, NE, NV, CA</t>
-  </si>
-  <si>
-    <t>https://www.bannerhealth.com/</t>
-  </si>
-  <si>
-    <t>insurance.report.json</t>
-  </si>
-  <si>
-    <t>insurance</t>
-  </si>
-  <si>
-    <t>2026-06-13T17:34:30.242Z</t>
-  </si>
-  <si>
-    <t>Planes y redes Banner | Banner Health</t>
-  </si>
-  <si>
-    <t>https://www.bannerhealth.com/insurance</t>
-  </si>
-  <si>
-    <t>kaiser-permanente.report.json</t>
-  </si>
-  <si>
-    <t>["hero","cards-feature"]</t>
-  </si>
-  <si>
-    <t>kaiser-permanente</t>
-  </si>
-  <si>
-    <t>breadcrumb-partner-content</t>
-  </si>
-  <si>
-    <t>2026-06-13T17:20:21.038Z</t>
-  </si>
-  <si>
-    <t>Kaiser Permanenete | Banner Health</t>
-  </si>
-  <si>
-    <t>https://www.bannerhealth.com/kaiser-permanente</t>
-  </si>
-  <si>
-    <t>locations.report.json</t>
-  </si>
-  <si>
-    <t>["search"]</t>
-  </si>
-  <si>
-    <t>locations</t>
-  </si>
-  <si>
-    <t>2026-06-13T17:20:14.706Z</t>
-  </si>
-  <si>
-    <t>Our Locations | Banner Health</t>
-  </si>
-  <si>
-    <t>https://www.bannerhealth.com/locations</t>
-  </si>
-  <si>
-    <t>medicare.report.json</t>
-  </si>
-  <si>
-    <t>["cards-feature","cards-feature","cards-feature","cards-feature","cards-feature","cards-feature"]</t>
-  </si>
-  <si>
-    <t>medicare</t>
-  </si>
-  <si>
-    <t>2026-06-12T20:24:01.268Z</t>
-  </si>
-  <si>
-    <t>Banner Medicare</t>
-  </si>
-  <si>
-    <t>https://www.bannerhealth.com/medicare</t>
-  </si>
-  <si>
-    <t>networkcolorado.report.json</t>
-  </si>
-  <si>
-    <t>["cards-feature","cards-feature"]</t>
-  </si>
-  <si>
-    <t>networkcolorado</t>
-  </si>
-  <si>
-    <t>cards-landing</t>
-  </si>
-  <si>
-    <t>2026-06-12T20:24:51.841Z</t>
-  </si>
-  <si>
-    <t>Banner Network Colorado</t>
-  </si>
-  <si>
-    <t>https://www.bannerhealth.com/networkcolorado</t>
-  </si>
-  <si>
-    <t>networksouth.report.json</t>
-  </si>
-  <si>
-    <t>["cards-feature","cards-feature","cards-feature"]</t>
-  </si>
-  <si>
-    <t>networksouth</t>
-  </si>
-  <si>
-    <t>2026-06-12T20:24:07.134Z</t>
-  </si>
-  <si>
-    <t>Banner Network Southern Arizona</t>
-  </si>
-  <si>
-    <t>https://www.bannerhealth.com/networksouth</t>
-  </si>
-  <si>
-    <t>newsroom.report.json</t>
-  </si>
-  <si>
-    <t>newsroom</t>
-  </si>
-  <si>
-    <t>2026-06-12T20:24:14.980Z</t>
-  </si>
-  <si>
-    <t>Banner Health | Newsroom and Media Resource Center</t>
-  </si>
-  <si>
-    <t>https://www.bannerhealth.com/newsroom</t>
-  </si>
-  <si>
-    <t>physician-directory.report.json</t>
-  </si>
-  <si>
-    <t>["search","cards-feature","cards-feature"]</t>
-  </si>
-  <si>
-    <t>physician-directory</t>
-  </si>
-  <si>
-    <t>2026-06-13T17:20:26.802Z</t>
-  </si>
-  <si>
-    <t>Find a Doctor</t>
-  </si>
-  <si>
-    <t>https://www.bannerhealth.com/physician-directory</t>
-  </si>
-  <si>
-    <t>search-results.report.json</t>
-  </si>
-  <si>
-    <t>search-results</t>
-  </si>
-  <si>
-    <t>2026-06-13T17:20:32.734Z</t>
-  </si>
-  <si>
-    <t>Banner Health Search Results | Banner Health</t>
-  </si>
-  <si>
-    <t>https://www.bannerhealth.com/search-results</t>
-  </si>
-  <si>
-    <t>services.report.json</t>
-  </si>
-  <si>
     <t>services</t>
   </si>
   <si>
     <t>hero-landing</t>
   </si>
   <si>
-    <t>2026-06-13T17:20:38.563Z</t>
+    <t>2026-06-13T17:58:18.326Z</t>
   </si>
   <si>
     <t>Services</t>
@@ -373,7 +382,7 @@
     <t>staying-well</t>
   </si>
   <si>
-    <t>2026-06-13T17:34:24.098Z</t>
+    <t>2026-06-13T17:56:52.423Z</t>
   </si>
   <si>
     <t>Ayúdame a estar bien | Banner Health</t>
@@ -388,7 +397,7 @@
     <t>es/about</t>
   </si>
   <si>
-    <t>2026-06-13T17:34:02.450Z</t>
+    <t>2026-06-13T17:56:19.733Z</t>
   </si>
   <si>
     <t>Acerca de Banner Health | Sistema líder de salud sin fines de lucro</t>
@@ -403,7 +412,7 @@
     <t>es/calendar</t>
   </si>
   <si>
-    <t>2026-06-13T17:35:09.920Z</t>
+    <t>2026-06-13T17:57:17.187Z</t>
   </si>
   <si>
     <t>Calendario de Eventos | Banner Health</t>
@@ -418,7 +427,7 @@
     <t>es/careers</t>
   </si>
   <si>
-    <t>2026-06-13T17:34:08.199Z</t>
+    <t>2026-06-13T17:56:25.415Z</t>
   </si>
   <si>
     <t>Carreras de atención médica</t>
@@ -433,7 +442,7 @@
     <t>es/contact-us</t>
   </si>
   <si>
-    <t>2026-06-13T17:34:54.256Z</t>
+    <t>2026-06-13T17:57:22.304Z</t>
   </si>
   <si>
     <t>Contáctenos | Banner Health</t>
@@ -451,7 +460,7 @@
     <t>breadcrumb-content</t>
   </si>
   <si>
-    <t>2026-06-13T17:34:43.159Z</t>
+    <t>2026-06-13T17:58:57.645Z</t>
   </si>
   <si>
     <t>https://www.bannerhealth.com/es/getcarenow</t>
@@ -460,16 +469,10 @@
     <t>es/healthcareblog.report.json</t>
   </si>
   <si>
-    <t>["carousel","cards-feature","cards-feature","cards-feature","cards-feature"]</t>
-  </si>
-  <si>
     <t>es/healthcareblog</t>
   </si>
   <si>
-    <t>service-detail-cards-carousel</t>
-  </si>
-  <si>
-    <t>2026-06-12T20:24:29.542Z</t>
+    <t>2026-06-14T21:01:01.496Z</t>
   </si>
   <si>
     <t>Blog de Banner Health</t>
@@ -484,7 +487,7 @@
     <t>es/kaiser-permanente</t>
   </si>
   <si>
-    <t>2026-06-13T17:34:37.143Z</t>
+    <t>2026-06-13T17:58:36.349Z</t>
   </si>
   <si>
     <t>Káiser Permanente | Banner Health</t>
@@ -499,7 +502,7 @@
     <t>es/locations</t>
   </si>
   <si>
-    <t>2026-06-13T17:35:03.037Z</t>
+    <t>2026-06-13T17:57:28.357Z</t>
   </si>
   <si>
     <t>Nuestras Ubicaciones | Banner Health</t>
@@ -514,7 +517,7 @@
     <t>es/medicare</t>
   </si>
   <si>
-    <t>2026-06-12T20:24:24.934Z</t>
+    <t>2026-06-13T17:58:07.541Z</t>
   </si>
   <si>
     <t>https://www.bannerhealth.com/es/medicare</t>
@@ -529,7 +532,7 @@
     <t>directory-breadcrumb</t>
   </si>
   <si>
-    <t>2026-06-13T17:35:20.866Z</t>
+    <t>2026-06-13T17:58:46.645Z</t>
   </si>
   <si>
     <t>Encuentre un médico</t>
@@ -559,7 +562,7 @@
     <t>es/services</t>
   </si>
   <si>
-    <t>2026-06-13T17:35:15.381Z</t>
+    <t>2026-06-13T17:58:25.038Z</t>
   </si>
   <si>
     <t>Servicios</t>
@@ -574,7 +577,7 @@
     <t>es/staying-well</t>
   </si>
   <si>
-    <t>2026-06-13T17:34:14.379Z</t>
+    <t>2026-06-13T17:56:31.441Z</t>
   </si>
   <si>
     <t>https://www.bannerhealth.com/es/staying-well</t>
@@ -1164,62 +1167,62 @@
         <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s">
         <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -1228,50 +1231,50 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -1280,24 +1283,24 @@
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -1306,50 +1309,50 @@
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -1358,24 +1361,24 @@
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -1384,102 +1387,102 @@
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G16" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H16" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G17" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H17" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F18" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F19" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G19" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H19" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B20" t="s">
         <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -1488,24 +1491,24 @@
         <v>12</v>
       </c>
       <c r="F20" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G20" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H20" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -1514,24 +1517,24 @@
         <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G21" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H21" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B22" t="s">
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -1540,24 +1543,24 @@
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G22" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H22" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>115</v>
       </c>
       <c r="C23" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -1566,24 +1569,24 @@
         <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G23" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H23" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B24" t="s">
         <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
@@ -1592,102 +1595,102 @@
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G24" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H24" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F25" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G25" t="s">
         <v>39</v>
       </c>
       <c r="H25" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="F26" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H26" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
@@ -1696,128 +1699,128 @@
         <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G28" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="F29" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G29" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F30" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G30" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F31" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H31" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>115</v>
       </c>
       <c r="C32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F32" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G32" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H32" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B33" t="s">
         <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -1826,13 +1829,13 @@
         <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G33" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
